--- a/data/Costa_Rica/output/resultados_lote_030_CR.xlsx
+++ b/data/Costa_Rica/output/resultados_lote_030_CR.xlsx
@@ -827,15 +827,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-fernanda-segura-903a551a3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -843,10 +843,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-fernanda-segura-903a551a3|90 ; https://cr.linkedin.com/in/fernanda-segura-68276a2aa|80 ; https://pe.linkedin.com/in/fernanda-segura-lee-687262328|80</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>503590484</t>
@@ -947,15 +963,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/randall-gonzalez-32794241</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -963,10 +979,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/randall-gonzalez-32794241|75</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>503590606</t>
@@ -1007,15 +1039,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/mirna-ruth-mart%C3%ADnez-33a7752a8</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1023,10 +1055,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/mirna-ruth-mart%C3%ADnez-33a7752a8|78</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>503590624</t>
@@ -1067,15 +1115,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/cindy-cristina-villalobos-villalobos-36816712b</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1083,10 +1131,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/cindy-cristina-villalobos-villalobos-36816712b|100</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>503590946</t>
@@ -1131,11 +1195,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1143,10 +1207,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/cindy-cristina-villalobos-villalobos-36816712b|100</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>503590946</t>
@@ -1187,26 +1267,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/tatiana-carrillo-11428a165</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/tatiana-carrillo-11428a165|80</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>503600008</t>
@@ -1251,22 +1347,38 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/tatiana-carrillo-11428a165|80</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>503600008</t>
@@ -1727,15 +1839,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/melissa-delgado-hernandez-9410883a</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1743,10 +1855,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-delgado-hernandez-9410883a|80 ; https://cr.linkedin.com/in/melissa-delgado-2333a31a6|80</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>503600206</t>
@@ -1791,11 +1919,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1803,10 +1931,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-delgado-hernandez-9410883a|80 ; https://cr.linkedin.com/in/melissa-delgado-2333a31a6|80</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>503600206</t>
@@ -1847,15 +1991,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://ar.linkedin.com/in/patricia-bustos-fierro-452b62a2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1863,10 +2007,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://ar.linkedin.com/in/patricia-bustos-fierro-452b62a2|90 ; https://ar.linkedin.com/in/patricia-bustos-73459916|80</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>503600218</t>
@@ -1911,11 +2071,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1923,10 +2083,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://ar.linkedin.com/in/patricia-bustos-fierro-452b62a2|90 ; https://ar.linkedin.com/in/patricia-bustos-73459916|80</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>503600218</t>
@@ -1967,15 +2143,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/ver%C3%B3nica-sandoval-3916175</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1983,10 +2159,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/ver%C3%B3nica-sandoval-3916175|75 ; https://www.linkedin.com/in/veronica-sandoval-msn-np-c-61aa8810a|75 ; https://ca.linkedin.com/in/veronica-sandoval-76538099|75</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>503600248</t>
@@ -2031,11 +2223,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2043,10 +2235,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/ver%C3%B3nica-sandoval-3916175|75 ; https://www.linkedin.com/in/veronica-sandoval-msn-np-c-61aa8810a|75 ; https://ca.linkedin.com/in/veronica-sandoval-76538099|75</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>503600248</t>
@@ -2087,15 +2295,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/ana-n%C3%BA%C3%B1ez-232625223/es</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2103,10 +2311,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/ana-n%C3%BA%C3%B1ez-232625223/es|80 ; https://pa.linkedin.com/in/ana-n%C3%BA%C3%B1ez-606825146|80 ; https://pa.linkedin.com/in/ana-n%C3%BA%C3%B1ez-berm%C3%BAdez-430675281|80</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>503600343</t>
@@ -2207,15 +2431,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/nazareth-diaz-664236315</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2223,10 +2447,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/nazareth-diaz-664236315|80 ; https://pa.linkedin.com/in/nazareth-morales-164614149|75</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>503610013</t>
@@ -2271,11 +2511,11 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2283,10 +2523,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/nazareth-diaz-664236315|80 ; https://pa.linkedin.com/in/nazareth-morales-164614149|75</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>503610013</t>
@@ -2331,11 +2587,11 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2343,10 +2599,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/nazareth-diaz-664236315|80 ; https://pa.linkedin.com/in/nazareth-morales-164614149|75</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>503610013</t>
@@ -2387,26 +2659,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-araya-52749371</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-araya-52749371|80 ; https://cr.linkedin.com/in/maria-araya-tristan-b62210a4|80</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>503610085</t>
@@ -2451,22 +2739,38 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-araya-52749371|80 ; https://cr.linkedin.com/in/maria-araya-tristan-b62210a4|80</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>503610085</t>
@@ -2507,26 +2811,42 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/melissa-chavarr%C3%ADa-67a7a31a6</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-chavarr%C3%ADa-67a7a31a6|83 ; https://cr.linkedin.com/in/melissa-villegas-a98747b6|78 ; https://cr.linkedin.com/in/melissa-villegas-g%C3%B3mez-751a7b107|75</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>503610136</t>
@@ -2571,22 +2891,38 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-chavarr%C3%ADa-67a7a31a6|80 ; https://cr.linkedin.com/in/melissa-villegas-a98747b6|75 ; https://cr.linkedin.com/in/melissa-villegas-g%C3%B3mez-751a7b107|75</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>503610136</t>
@@ -2631,22 +2967,38 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-chavarr%C3%ADa-67a7a31a6|80 ; https://cr.linkedin.com/in/melissa-villegas-a98747b6|75 ; https://cr.linkedin.com/in/melissa-villegas-g%C3%B3mez-751a7b107|75</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>503610136</t>
@@ -2687,15 +3039,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/luis-guti%C3%A9rrez-a6a160300</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2703,10 +3055,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/luis-guti%C3%A9rrez-a6a160300|80 ; https://co.linkedin.com/in/luis-guti%C3%A9rrez-0457561a8|80 ; https://cr.linkedin.com/in/luis-gutierrez-8ab42262|80</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>503610171</t>
@@ -2751,11 +3119,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2763,10 +3131,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/luis-guti%C3%A9rrez-a6a160300|80 ; https://co.linkedin.com/in/luis-guti%C3%A9rrez-0457561a8|80 ; https://cr.linkedin.com/in/luis-gutierrez-8ab42262|80</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>503610171</t>
@@ -2807,15 +3191,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/huberth-campos-09a49864</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2823,10 +3207,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/huberth-campos-09a49864|80 ; https://www.linkedin.com/in/luis-campos-15b09892|80 ; https://cr.linkedin.com/in/ing-luis-campos|80</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>503610342</t>
@@ -2867,15 +3267,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/yessenia-ruiz-a-347b09124</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2883,10 +3283,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yessenia-ruiz-a-347b09124|80 ; https://mx.linkedin.com/in/maria-ruiz-289a57111|80 ; https://pa.linkedin.com/in/maria-ruiz-2402854b|80</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>503610550</t>
@@ -2931,11 +3347,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2943,10 +3359,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yessenia-ruiz-a-347b09124|80 ; https://mx.linkedin.com/in/maria-ruiz-289a57111|80 ; https://pa.linkedin.com/in/maria-ruiz-2402854b|80</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>503610550</t>
@@ -2987,15 +3419,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mariana-espinoza-chacon-9b02229a</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3003,10 +3435,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mariana-espinoza-chacon-9b02229a|100 ; https://mx.linkedin.com/in/mariana-martinez-espinoza-88131b1b0|80</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>503610596</t>
@@ -3047,15 +3495,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://ie.linkedin.com/in/daniela-chaves-leiton-a25a961a7</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3063,10 +3511,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/in/daniela-chaves-leiton-a25a961a7|100 ; https://cr.linkedin.com/in/daniela-chaves-artavia-498880146|80 ; https://cr.linkedin.com/in/daniela-chaves-rosales-ab487351|80</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>503610645</t>
@@ -3107,15 +3571,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/carolina-hernandez-bola%C3%B1os-827128a9</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3123,10 +3587,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/carolina-hernandez-bola%C3%B1os-827128a9|80 ; https://www.linkedin.com/in/carolina-hernandez-41027a139/es|80 ; https://www.linkedin.com/in/carolina-hern%C3%A1ndez-mora-9a11a1239/en|80</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>503610689</t>
@@ -3171,11 +3651,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3183,10 +3663,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/carolina-hernandez-bola%C3%B1os-827128a9|80 ; https://www.linkedin.com/in/carolina-hernandez-41027a139/es|80 ; https://www.linkedin.com/in/carolina-hern%C3%A1ndez-mora-9a11a1239/en|80</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>503610689</t>
@@ -3287,26 +3783,42 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/marcela-ara%C3%BAz-0388b7225</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/marcela-ara%C3%BAz-0388b7225|75 ; https://pa.linkedin.com/in/marcela-arauz-quintero-1428a9150|75</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>503610986</t>
@@ -3347,26 +3859,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/roger-araya-0845451a</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/roger-araya-0845451a|80</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>503610997</t>
@@ -3407,15 +3935,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/johan-g%C3%B3mez-61a843299</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3423,10 +3951,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/johan-g%C3%B3mez-61a843299|80</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>503620012</t>
@@ -3527,15 +4071,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/manuel-fonseca-887191312</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3543,10 +4087,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/manuel-fonseca-887191312|80 ; https://pa.linkedin.com/in/manuel-fonseca-167982210|80 ; https://mx.linkedin.com/in/victor-manuel-fonseca-596ab0256|80</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>503620194</t>
@@ -3591,11 +4151,11 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3603,10 +4163,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/manuel-fonseca-887191312|80 ; https://pa.linkedin.com/in/manuel-fonseca-167982210|80 ; https://mx.linkedin.com/in/victor-manuel-fonseca-596ab0256|80</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>503620194</t>
@@ -3651,11 +4227,11 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3663,10 +4239,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/manuel-fonseca-887191312|80 ; https://pa.linkedin.com/in/manuel-fonseca-167982210|80 ; https://mx.linkedin.com/in/victor-manuel-fonseca-596ab0256|80</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>503620194</t>
@@ -3707,15 +4299,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/juan-carlos-chaves-cerdas-69373924</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3723,10 +4315,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/juan-carlos-chaves-cerdas-69373924|100 ; https://cr.linkedin.com/in/juan-carlos-chaves-363522159|90 ; https://cr.linkedin.com/in/juan-carlos-chaves-a5000972|90</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>503620577</t>
@@ -4007,15 +4615,15 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/natalia-porras-bol%C3%ADvar-6b8619b8</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4023,10 +4631,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/natalia-porras-bol%C3%ADvar-6b8619b8|100 ; https://cr.linkedin.com/in/natalia-porras-zamora-70913329a|80</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>503620675</t>
@@ -4067,15 +4691,15 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-vega-42427327</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4083,10 +4707,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-vega-42427327|80 ; https://pa.linkedin.com/in/maria-vega-vergara-08ab0281|80 ; https://cr.linkedin.com/in/mar%C3%ADa-vega-arias-b19b1713a|80</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>503620758</t>
@@ -4131,11 +4771,11 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4143,10 +4783,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-vega-42427327|80 ; https://pa.linkedin.com/in/maria-vega-vergara-08ab0281|80 ; https://cr.linkedin.com/in/mar%C3%ADa-vega-arias-b19b1713a|80</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>503620758</t>
@@ -4187,15 +4843,15 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/emmanuel-brenes-6a42b838</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4203,10 +4859,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/emmanuel-brenes-6a42b838|80</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>503620790</t>
@@ -4247,15 +4919,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-quesada-alfaro-670b62230</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4263,10 +4935,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-quesada-alfaro-670b62230|83 ; https://cr.linkedin.com/in/maria-alfaro-2241a756|80 ; https://www.linkedin.com/in/maria-alfaro-2b8439360|80</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>503620800</t>
@@ -4311,11 +4999,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4323,10 +5011,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-quesada-alfaro-670b62230|83 ; https://cr.linkedin.com/in/maria-alfaro-2241a756|80 ; https://www.linkedin.com/in/maria-alfaro-2b8439360|80</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>503620800</t>
@@ -4367,15 +5071,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/marabely-l%C3%B3pez-solano-86350625</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4383,10 +5087,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/marabely-l%C3%B3pez-solano-86350625|100</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>503620828</t>
@@ -4427,15 +5147,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/jos%C3%A9-gallo-lo%C3%A1iciga-477623228</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4443,10 +5163,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/jos%C3%A9-gallo-lo%C3%A1iciga-477623228|100</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>503620945</t>
@@ -4487,15 +5223,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/adriana-cantillano-9b0228108</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4503,10 +5239,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adriana-cantillano-9b0228108|80 ; https://cr.linkedin.com/in/adriana-arias-258653134|75 ; https://pa.linkedin.com/in/adriana-arias-100810373|75</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>503630075</t>
@@ -4551,11 +5303,11 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4563,10 +5315,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adriana-cantillano-9b0228108|80 ; https://cr.linkedin.com/in/adriana-arias-258653134|75 ; https://pa.linkedin.com/in/adriana-arias-100810373|75</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>503630075</t>
@@ -4607,15 +5375,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diana-bonilla-arce-b52537176</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4623,10 +5391,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-bonilla-arce-b52537176|86 ; https://cr.linkedin.com/in/diana-bonilla-968360198|80 ; https://www.linkedin.com/in/diana-bonilla-96102673|80</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>503630078</t>
@@ -4671,11 +5455,11 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4683,10 +5467,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-bonilla-arce-b52537176|86 ; https://cr.linkedin.com/in/diana-bonilla-968360198|80 ; https://www.linkedin.com/in/diana-bonilla-96102673|80</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>503630078</t>
@@ -4727,15 +5527,15 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diana-bonilla-968360198</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4743,10 +5543,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-bonilla-968360198|80 ; https://www.linkedin.com/in/diana-bonilla-96102673|80 ; https://cr.linkedin.com/in/diana-bonilla-arce-b52537176|80</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>503630078</t>
@@ -4791,11 +5607,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4803,10 +5619,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-bonilla-968360198|80 ; https://www.linkedin.com/in/diana-bonilla-96102673|80 ; https://cr.linkedin.com/in/diana-bonilla-arce-b52537176|80</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>503630078</t>
@@ -5027,15 +5859,15 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/kevin-gutierrez-54a58a188</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5043,10 +5875,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/kevin-gutierrez-54a58a188|80 ; https://cr.linkedin.com/in/andres-gutierrez-348232116|80 ; https://ec.linkedin.com/in/andr%C3%A9s-guti%C3%A9rrez-le%C3%B3n-975a4424|80</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>503630148</t>
@@ -5147,15 +5995,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/stephany-chavarria-rojas-847b8a2a</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5163,10 +6011,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/stephany-chavarria-rojas-847b8a2a|86</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>503630384</t>
@@ -5211,11 +6075,11 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5223,10 +6087,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/stephany-chavarria-rojas-847b8a2a|86</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>503630384</t>
@@ -5447,15 +6327,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/joselyn-rojas-332744bb</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5463,10 +6343,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/joselyn-rojas-332744bb|80 ; https://cr.linkedin.com/in/joselyn-rojas-7a43a91a6|80 ; https://cr.linkedin.com/in/joselyn-rojas-209b59159|80</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>503630521</t>
@@ -5507,15 +6403,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/massiel-corea-badilla-0928aa1b0</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5523,10 +6419,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/massiel-corea-badilla-0928aa1b0|100</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>503630530</t>
@@ -5571,11 +6483,11 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5583,10 +6495,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/massiel-corea-badilla-0928aa1b0|100</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>503630530</t>
@@ -5807,26 +6735,42 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/hanzel-almanza-rojas-9b943618</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/hanzel-almanza-rojas-9b943618|100</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>503630743</t>
@@ -5871,22 +6815,38 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/hanzel-almanza-rojas-9b943618|100</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>503630743</t>
@@ -5927,15 +6887,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-villalobos-a7a10b124</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5943,10 +6903,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-villalobos-a7a10b124|80 ; https://www.linkedin.com/in/maria-villalobos-b73ba3127|80 ; https://cr.linkedin.com/in/maria-villalobos-b06890174|80</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>503640032</t>
@@ -5987,15 +6963,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/christian-castillo-fern%C3%A1ndez-1b968570</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6003,10 +6979,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/christian-castillo-fern%C3%A1ndez-1b968570|75 ; https://cr.linkedin.com/in/christian-castillo-fern%C3%A1ndez-02610448|75 ; https://cr.linkedin.com/in/christian-castillo-delgado-a4811575|75</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>503640337</t>
@@ -6047,15 +7039,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/javier-fonseca-800b032b</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6063,10 +7055,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/javier-leiva-sanchez-99291453|84 ; https://cr.linkedin.com/in/javier-fonseca-800b032b|80</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>503640382</t>
@@ -6167,15 +7175,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/ginneth-gonz%C3%A1lez-artavia-a8033778</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6183,10 +7191,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ginneth-gonz%C3%A1lez-artavia-a8033778|100</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>503640560</t>
@@ -6407,15 +7431,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-edith-arrieta-ortiz-213abb6b</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6423,10 +7447,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-edith-arrieta-ortiz-213abb6b|100</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>503640660</t>
@@ -6471,11 +7511,11 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6483,10 +7523,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-edith-arrieta-ortiz-213abb6b|100</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>503640660</t>
@@ -6707,15 +7763,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/gustavo-pe%C3%B1a-arrieta-350082213</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6723,10 +7779,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/gustavo-pe%C3%B1a-arrieta-350082213|100 ; https://cr.linkedin.com/in/gustavo-pe%C3%B1a-s%C3%A1nchez-b4029715b|80</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>503640852</t>
@@ -6947,15 +8019,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-arroyo-s%C3%A1nchez-47895a39</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6963,10 +8035,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-arroyo-s%C3%A1nchez-47895a39|80</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>503650058</t>
@@ -7007,15 +8095,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/zoila-del-castillo-1955b449</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7023,10 +8111,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zoila-del-castillo-1955b449|90 ; https://www.linkedin.com/in/gina-del-castillo-ba56aa14b|80 ; https://pa.linkedin.com/in/maria-castillo-630793212|80</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>503650114</t>
@@ -7067,26 +8171,42 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/fabio-ballestero-81a9a0a1</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>ESTUDIÓ</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/fabio-ballestero-81a9a0a1|90 ; https://cr.linkedin.com/in/fabio-ballestero-80272971|83</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>503650164</t>
@@ -7127,26 +8247,42 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/daniela-rivera-sandoval-0958aa242</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+          <t>ESTUDIÓ</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/daniela-rivera-sandoval-0958aa242|80 ; https://pa.linkedin.com/in/daniela-rivera-95661b263|80 ; https://cr.linkedin.com/in/daniela-rivera-8b366280|80</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>503650570</t>
@@ -7247,15 +8383,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/katherine-garcia-molina-197492293</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7263,10 +8399,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/katherine-garcia-molina-197492293|100</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>503660009</t>
@@ -7307,26 +8459,42 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/isabel-quir%C3%B3s-sol%C3%ADs-96982b11b</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/isabel-quir%C3%B3s-sol%C3%ADs-96982b11b|80</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>503660064</t>
@@ -7367,15 +8535,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/tatiana-soto-mej%C3%ADa-a863b91a1</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7383,10 +8551,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/tatiana-soto-mej%C3%ADa-a863b91a1|80 ; https://cr.linkedin.com/in/tatiana-chavarr%C3%ADa-655a02153|75 ; https://cr.linkedin.com/in/tatiana-chavarr%C3%ADa-caracas-8b2499161|75</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>503660074</t>
@@ -7487,15 +8671,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/antonio-rodr%C3%ADguez-64600a360</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7503,10 +8687,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/antonio-rodr%C3%ADguez-64600a360|80 ; https://pa.linkedin.com/in/antonio-rodr%C3%ADguez-7415471a9|80 ; https://www.linkedin.com/in/antonio-rodriguez-camps|80</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>503660252</t>
@@ -7547,15 +8747,15 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cl.linkedin.com/in/daniela-granados-3b139535a/en</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7563,10 +8763,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://cl.linkedin.com/in/daniela-granados-3b139535a/en|80 ; https://cl.linkedin.com/in/daniela-granados-3b139535a|80 ; https://cr.linkedin.com/in/daniela-granados-teer-047b39235|80</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>503660406</t>
@@ -7607,15 +8823,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/marco-alvarez-8726b930b/es</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7623,10 +8839,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/marco-alvarez-8726b930b/es|80 ; https://pa.linkedin.com/in/marco-%C3%A1lvarez-122648319|80 ; https://cr.linkedin.com/in/marco-alvarez-8726b930b/pt|80</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>503660577</t>
@@ -7727,15 +8959,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/julissa-solera-mondrag%C3%B3n-3b383978</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7743,10 +8975,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/julissa-solera-mondrag%C3%B3n-3b383978|100</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>503660779</t>
@@ -7791,11 +9039,11 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7803,10 +9051,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/julissa-solera-mondrag%C3%B3n-3b383978|100</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>503660779</t>
@@ -7847,15 +9111,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-vargas-47073a125</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7863,10 +9127,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-vargas-1bb100379|83 ; https://cr.linkedin.com/in/maria-vargas-78b279134|83 ; https://cr.linkedin.com/in/maria-vargas-676642103|83</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>503660799</t>
@@ -7907,15 +9187,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/andrea-jim%C3%A9nez-leit%C3%B3n-b62512271</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7923,10 +9203,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/andrea-jim%C3%A9nez-leit%C3%B3n-b62512271|83 ; https://cr.linkedin.com/in/andrea-jim%C3%A9nez-5a022322|80 ; https://cr.linkedin.com/in/andrea-jim%C3%A9nez-88505460|80</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>503660905</t>
@@ -7967,26 +9263,42 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/daniela-mora-a60736379</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/daniela-mora-a60736379|80 ; https://cr.linkedin.com/in/daniela-mora-2b26a52b6|80 ; https://cr.linkedin.com/in/daniela-mora-cort%C3%A9s-992219294|80</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>503670008</t>
@@ -8031,22 +9343,38 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/daniela-rojas-alfaro-2a69a2134|90 ; https://cr.linkedin.com/in/daniela-mora-a60736379|80 ; https://cr.linkedin.com/in/daniela-mora-2b26a52b6|80</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>503670008</t>
@@ -8267,15 +9595,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/berlin-lopez-herra-9aa30285</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8283,10 +9611,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/berlin-lopez-herra-9aa30285|100</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>503670186</t>
@@ -8327,26 +9671,42 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/karen-morales-sandi-770138115</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/karen-morales-sandi-770138115|75 ; https://cr.linkedin.com/in/karen-morales-54651a7a|75</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>503670373</t>
@@ -8391,22 +9751,38 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/karen-morales-sandi-770138115|75 ; https://cr.linkedin.com/in/karen-morales-54651a7a|75</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>503670373</t>
@@ -8507,15 +9883,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/arlene-rojas-rodriguez-4960b6278?trk=people-guest_people_search-card</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8523,10 +9899,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/arlene-rojas-rodriguez-4960b6278?trk=people-guest_people_search-card|100 ; https://cr.linkedin.com/in/arlene-rodr%C3%ADguez-naranjo-b070602a|80</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>503670775</t>
@@ -8567,15 +9959,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-jose-ortega-62498a61</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8583,10 +9975,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-jose-ortega-62498a61|80 ; https://pa.linkedin.com/in/jose-ortega-889658152|80 ; https://pa.linkedin.com/in/juan-jose-ortega-8864762a5|80</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>503670778</t>
@@ -8627,15 +10035,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-paniagua-meza-a15321195</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8643,10 +10051,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-paniagua-meza-a15321195|80</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>503670842</t>
@@ -8687,15 +10111,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-carrillo-osorno-3676476b</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8703,10 +10127,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-carrillo-osorno-3676476b|100 ; https://www.linkedin.com/in/maria-carrillo-578214141|80</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>503680088</t>
@@ -8751,11 +10191,11 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8763,10 +10203,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-carrillo-osorno-3676476b|100 ; https://www.linkedin.com/in/maria-carrillo-578214141|80</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>503680088</t>
@@ -8807,15 +10263,15 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/adrian-gutierrez-6078003b3</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8823,10 +10279,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adrian-gutierrez-6078003b3|80 ; https://pa.linkedin.com/in/adri%C3%A1n-guti%C3%A9rrez-madrid-35b5b8235|80 ; https://cr.linkedin.com/in/adrian-gutierrez-533394308|80</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>503680103</t>
@@ -8871,11 +10343,11 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8883,10 +10355,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adrian-gutierrez-6078003b3|80 ; https://pa.linkedin.com/in/adri%C3%A1n-guti%C3%A9rrez-madrid-35b5b8235|80 ; https://cr.linkedin.com/in/adrian-gutierrez-533394308|80</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>503680103</t>
@@ -8927,15 +10415,15 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://co.linkedin.com/in/carolina-vargas-g%C3%B3mez-8a2633184</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8943,10 +10431,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/in/carolina-vargas-g%C3%B3mez-8a2633184|90 ; https://cr.linkedin.com/in/carolina-vargas-cruz-91b748290|78 ; https://mx.linkedin.com/in/carolina-vargas-825491115/en|78</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>NO COINCIDE</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>503680509</t>
@@ -8987,15 +10491,15 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/estefany-quesada-17495176</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9003,10 +10507,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/estefany-quesada-17495176|80</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>503680537</t>
@@ -9047,15 +10567,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/yahaira-p%C3%A9rez-289aa261</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9063,10 +10583,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yahaira-p%C3%A9rez-289aa261|80</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>503680671</t>
@@ -9111,11 +10647,11 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9123,10 +10659,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yahaira-p%C3%A9rez-289aa261|80</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>503680671</t>
@@ -9167,26 +10719,42 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/leonardo-venegas-9814b5276</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/leonardo-venegas-9814b5276|80 ; https://co.linkedin.com/in/leonardo-venegas-tinjac%C3%A1-4717956b|80</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>503680856</t>
@@ -9347,15 +10915,15 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/mar%C3%ADa-mendez-987b7b135</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9363,10 +10931,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mar%C3%ADa-mendez-987b7b135|80 ; https://www.linkedin.com/in/maria-mendez-ea-b92722256|60</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>503690096</t>
@@ -9411,11 +10995,11 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9423,10 +11007,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mar%C3%ADa-mendez-987b7b135|80 ; https://www.linkedin.com/in/maria-mendez-ea-b92722256|60</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>503690096</t>
@@ -9467,15 +11067,15 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/raquel-campos-9b907475</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9483,10 +11083,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/raquel-campos-9b907475|80 ; https://cr.linkedin.com/in/raquel-campos-solorzano-63b170195|80</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>503690099</t>
@@ -9527,15 +11143,15 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://hn.linkedin.com/in/juan-ordo%C3%B1ez-5baa0a2b6</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9543,10 +11159,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://hn.linkedin.com/in/juan-ordo%C3%B1ez-5baa0a2b6|100</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>503690224</t>
